--- a/000-要件定義/003-WBS.xlsx
+++ b/000-要件定義/003-WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF0BD0-4089-4A80-BC43-0C3E3F40FC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214245D6-B711-4BA9-9BBA-752BE08F08DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,7 +589,7 @@
     <numFmt numFmtId="177" formatCode="yyyy/mm"/>
     <numFmt numFmtId="178" formatCode="aaa"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="明朝"/>
@@ -624,6 +624,13 @@
     <font>
       <sz val="8"/>
       <color rgb="FFFFFF00"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2049,7 +2056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2505,12 +2512,129 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2529,11 +2653,158 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2541,18 +2812,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2574,12 +2833,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2592,247 +2845,85 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2866,87 +2957,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3666,94 +3676,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="235" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="238" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="193" t="s">
+      <c r="C1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="199" t="s">
+      <c r="D1" s="242"/>
+      <c r="E1" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="202" t="s">
+      <c r="F1" s="250" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="184">
+      <c r="G1" s="232">
         <v>45536</v>
       </c>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="185"/>
-      <c r="P1" s="185"/>
-      <c r="Q1" s="185"/>
-      <c r="R1" s="185"/>
-      <c r="S1" s="185"/>
-      <c r="T1" s="185"/>
-      <c r="U1" s="185"/>
-      <c r="V1" s="185"/>
-      <c r="W1" s="185"/>
-      <c r="X1" s="185"/>
-      <c r="Y1" s="185"/>
-      <c r="Z1" s="185"/>
-      <c r="AA1" s="185"/>
-      <c r="AB1" s="185"/>
-      <c r="AC1" s="185"/>
-      <c r="AD1" s="185"/>
-      <c r="AE1" s="185"/>
-      <c r="AF1" s="185"/>
-      <c r="AG1" s="185"/>
-      <c r="AH1" s="185"/>
-      <c r="AI1" s="185"/>
-      <c r="AJ1" s="186"/>
-      <c r="AK1" s="184">
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
+      <c r="S1" s="233"/>
+      <c r="T1" s="233"/>
+      <c r="U1" s="233"/>
+      <c r="V1" s="233"/>
+      <c r="W1" s="233"/>
+      <c r="X1" s="233"/>
+      <c r="Y1" s="233"/>
+      <c r="Z1" s="233"/>
+      <c r="AA1" s="233"/>
+      <c r="AB1" s="233"/>
+      <c r="AC1" s="233"/>
+      <c r="AD1" s="233"/>
+      <c r="AE1" s="233"/>
+      <c r="AF1" s="233"/>
+      <c r="AG1" s="233"/>
+      <c r="AH1" s="233"/>
+      <c r="AI1" s="233"/>
+      <c r="AJ1" s="234"/>
+      <c r="AK1" s="232">
         <v>45566</v>
       </c>
-      <c r="AL1" s="185"/>
-      <c r="AM1" s="185"/>
-      <c r="AN1" s="185"/>
-      <c r="AO1" s="185"/>
-      <c r="AP1" s="185"/>
-      <c r="AQ1" s="185"/>
-      <c r="AR1" s="185"/>
-      <c r="AS1" s="185"/>
-      <c r="AT1" s="185"/>
-      <c r="AU1" s="185"/>
-      <c r="AV1" s="185"/>
-      <c r="AW1" s="185"/>
-      <c r="AX1" s="185"/>
-      <c r="AY1" s="185"/>
-      <c r="AZ1" s="185"/>
-      <c r="BA1" s="185"/>
-      <c r="BB1" s="185"/>
-      <c r="BC1" s="185"/>
-      <c r="BD1" s="185"/>
-      <c r="BE1" s="185"/>
-      <c r="BF1" s="185"/>
-      <c r="BG1" s="185"/>
-      <c r="BH1" s="185"/>
-      <c r="BI1" s="185"/>
-      <c r="BJ1" s="185"/>
-      <c r="BK1" s="185"/>
-      <c r="BL1" s="185"/>
-      <c r="BM1" s="185"/>
-      <c r="BN1" s="186"/>
+      <c r="AL1" s="233"/>
+      <c r="AM1" s="233"/>
+      <c r="AN1" s="233"/>
+      <c r="AO1" s="233"/>
+      <c r="AP1" s="233"/>
+      <c r="AQ1" s="233"/>
+      <c r="AR1" s="233"/>
+      <c r="AS1" s="233"/>
+      <c r="AT1" s="233"/>
+      <c r="AU1" s="233"/>
+      <c r="AV1" s="233"/>
+      <c r="AW1" s="233"/>
+      <c r="AX1" s="233"/>
+      <c r="AY1" s="233"/>
+      <c r="AZ1" s="233"/>
+      <c r="BA1" s="233"/>
+      <c r="BB1" s="233"/>
+      <c r="BC1" s="233"/>
+      <c r="BD1" s="233"/>
+      <c r="BE1" s="233"/>
+      <c r="BF1" s="233"/>
+      <c r="BG1" s="233"/>
+      <c r="BH1" s="233"/>
+      <c r="BI1" s="233"/>
+      <c r="BJ1" s="233"/>
+      <c r="BK1" s="233"/>
+      <c r="BL1" s="233"/>
+      <c r="BM1" s="233"/>
+      <c r="BN1" s="234"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="188"/>
-      <c r="B2" s="191"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="203"/>
+      <c r="A2" s="236"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="243"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="251"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -3995,12 +4005,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="189"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="204"/>
+      <c r="A3" s="237"/>
+      <c r="B3" s="240"/>
+      <c r="C3" s="245"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -4183,20 +4193,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="175">
+      <c r="A4" s="259">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="176" t="s">
+      <c r="C4" s="260" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="177"/>
-      <c r="E4" s="180" t="s">
+      <c r="D4" s="261"/>
+      <c r="E4" s="262" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="182" t="s">
+      <c r="F4" s="264" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="93"/>
@@ -4261,12 +4271,12 @@
       <c r="BN4" s="69"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="166"/>
+      <c r="A5" s="254"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="181"/>
-      <c r="F5" s="183"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="263"/>
+      <c r="F5" s="265"/>
       <c r="G5" s="95"/>
       <c r="H5" s="62"/>
       <c r="I5" s="62"/>
@@ -4329,18 +4339,18 @@
       <c r="BN5" s="70"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="165">
+      <c r="A6" s="253">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="168"/>
-      <c r="E6" s="171" t="s">
+      <c r="D6" s="174"/>
+      <c r="E6" s="255" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="173" t="s">
+      <c r="F6" s="257" t="s">
         <v>45</v>
       </c>
       <c r="G6" s="51"/>
@@ -4405,12 +4415,12 @@
       <c r="BN6" s="71"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="166"/>
+      <c r="A7" s="254"/>
       <c r="B7" s="96"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="174"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="256"/>
+      <c r="F7" s="258"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
@@ -4473,20 +4483,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="207">
+      <c r="A8" s="159">
         <v>3</v>
       </c>
       <c r="B8" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="208" t="s">
+      <c r="C8" s="209" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="209"/>
-      <c r="E8" s="232" t="s">
+      <c r="D8" s="210"/>
+      <c r="E8" s="230" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="205" t="s">
+      <c r="F8" s="191" t="s">
         <v>58</v>
       </c>
       <c r="G8" s="38"/>
@@ -4551,12 +4561,12 @@
       <c r="BN8" s="73"/>
     </row>
     <row r="9" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A9" s="164"/>
+      <c r="A9" s="166"/>
       <c r="B9" s="107"/>
-      <c r="C9" s="230"/>
-      <c r="D9" s="231"/>
-      <c r="E9" s="233"/>
-      <c r="F9" s="206"/>
+      <c r="C9" s="228"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="208"/>
       <c r="G9" s="113"/>
       <c r="H9" s="114"/>
       <c r="I9" s="114"/>
@@ -4619,16 +4629,16 @@
       <c r="BN9" s="118"/>
     </row>
     <row r="10" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A10" s="215"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="107"/>
-      <c r="C10" s="217" t="s">
+      <c r="C10" s="215" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="227"/>
-      <c r="E10" s="223" t="s">
+      <c r="D10" s="225"/>
+      <c r="E10" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="224" t="s">
+      <c r="F10" s="222" t="s">
         <v>58</v>
       </c>
       <c r="G10" s="133"/>
@@ -4693,12 +4703,12 @@
       <c r="BN10" s="138"/>
     </row>
     <row r="11" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A11" s="216"/>
+      <c r="A11" s="214"/>
       <c r="B11" s="107"/>
-      <c r="C11" s="228"/>
-      <c r="D11" s="229"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="225"/>
+      <c r="C11" s="226"/>
+      <c r="D11" s="227"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="223"/>
       <c r="G11" s="108"/>
       <c r="H11" s="109"/>
       <c r="I11" s="109"/>
@@ -4761,16 +4771,16 @@
       <c r="BN11" s="131"/>
     </row>
     <row r="12" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A12" s="215"/>
+      <c r="A12" s="213"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="217" t="s">
+      <c r="C12" s="215" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="218"/>
-      <c r="E12" s="221" t="s">
+      <c r="D12" s="216"/>
+      <c r="E12" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="224" t="s">
+      <c r="F12" s="222" t="s">
         <v>58</v>
       </c>
       <c r="G12" s="120"/>
@@ -4835,12 +4845,12 @@
       <c r="BN12" s="70"/>
     </row>
     <row r="13" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A13" s="216"/>
+      <c r="A13" s="214"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="219"/>
-      <c r="D13" s="220"/>
-      <c r="E13" s="222"/>
-      <c r="F13" s="226"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="218"/>
+      <c r="E13" s="220"/>
+      <c r="F13" s="224"/>
       <c r="G13" s="124"/>
       <c r="H13" s="125"/>
       <c r="I13" s="126"/>
@@ -4903,20 +4913,20 @@
       <c r="BN13" s="74"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="207">
+      <c r="A14" s="159">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="208" t="s">
+      <c r="C14" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="209"/>
-      <c r="E14" s="212" t="s">
+      <c r="D14" s="210"/>
+      <c r="E14" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="213" t="s">
+      <c r="F14" s="207" t="s">
         <v>58</v>
       </c>
       <c r="G14" s="50"/>
@@ -4981,12 +4991,12 @@
       <c r="BN14" s="70"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="164"/>
+      <c r="A15" s="166"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="214"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="190"/>
+      <c r="F15" s="192"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -5049,18 +5059,18 @@
       <c r="BN15" s="70"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="163">
+      <c r="A16" s="158">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="168"/>
-      <c r="E16" s="155" t="s">
+      <c r="D16" s="174"/>
+      <c r="E16" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="236" t="s">
+      <c r="F16" s="194" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="51"/>
@@ -5125,12 +5135,12 @@
       <c r="BN16" s="71"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="207"/>
+      <c r="A17" s="159"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="235"/>
-      <c r="E17" s="212"/>
-      <c r="F17" s="213"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="187"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="207"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -5193,20 +5203,20 @@
       <c r="BN17" s="72"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="237">
+      <c r="A18" s="202">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="239"/>
-      <c r="E18" s="240" t="s">
+      <c r="D18" s="185"/>
+      <c r="E18" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="205" t="s">
+      <c r="F18" s="191" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="38"/>
@@ -5271,12 +5281,12 @@
       <c r="BN18" s="73"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="237"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="179"/>
-      <c r="E19" s="156"/>
-      <c r="F19" s="214"/>
+      <c r="C19" s="188"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="190"/>
+      <c r="F19" s="192"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -5339,18 +5349,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="237">
+      <c r="A20" s="202">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="167" t="s">
+      <c r="C20" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="168"/>
-      <c r="E20" s="241" t="s">
+      <c r="D20" s="174"/>
+      <c r="E20" s="193" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="236" t="s">
+      <c r="F20" s="194" t="s">
         <v>59</v>
       </c>
       <c r="G20" s="51"/>
@@ -5415,12 +5425,12 @@
       <c r="BN20" s="71"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="237"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="178"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="214"/>
+      <c r="C21" s="188"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="190"/>
+      <c r="F21" s="192"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5483,18 +5493,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="237">
+      <c r="A22" s="202">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="167" t="s">
+      <c r="C22" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="168"/>
-      <c r="E22" s="241" t="s">
+      <c r="D22" s="174"/>
+      <c r="E22" s="193" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="236" t="s">
+      <c r="F22" s="194" t="s">
         <v>59</v>
       </c>
       <c r="G22" s="52"/>
@@ -5559,12 +5569,12 @@
       <c r="BN22" s="75"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="237"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="169"/>
-      <c r="D23" s="170"/>
-      <c r="E23" s="242"/>
-      <c r="F23" s="243"/>
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="204"/>
+      <c r="F23" s="205"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5627,20 +5637,20 @@
       <c r="BN23" s="76"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="163">
+      <c r="A24" s="158">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="238" t="s">
+      <c r="C24" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="239"/>
-      <c r="E24" s="240" t="s">
+      <c r="D24" s="185"/>
+      <c r="E24" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="205"/>
+      <c r="F24" s="191"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5703,14 +5713,14 @@
       <c r="BN24" s="77"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="164"/>
+      <c r="A25" s="166"/>
       <c r="B25" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="178"/>
-      <c r="D25" s="179"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="214"/>
+      <c r="C25" s="188"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="190"/>
+      <c r="F25" s="192"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5773,18 +5783,18 @@
       <c r="BN25" s="78"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="163">
+      <c r="A26" s="158">
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="159" t="s">
+      <c r="C26" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="160"/>
-      <c r="E26" s="155" t="s">
+      <c r="D26" s="199"/>
+      <c r="E26" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="157"/>
+      <c r="F26" s="196"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5847,12 +5857,12 @@
       <c r="BN26" s="78"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="164"/>
+      <c r="A27" s="166"/>
       <c r="B27" s="36"/>
-      <c r="C27" s="161"/>
-      <c r="D27" s="162"/>
-      <c r="E27" s="156"/>
-      <c r="F27" s="158"/>
+      <c r="C27" s="200"/>
+      <c r="D27" s="201"/>
+      <c r="E27" s="190"/>
+      <c r="F27" s="197"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5915,18 +5925,18 @@
       <c r="BN27" s="78"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="163">
+      <c r="A28" s="158">
         <v>11</v>
       </c>
       <c r="B28" s="36"/>
-      <c r="C28" s="159" t="s">
+      <c r="C28" s="198" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="160"/>
-      <c r="E28" s="155" t="s">
+      <c r="D28" s="199"/>
+      <c r="E28" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="157"/>
+      <c r="F28" s="196"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5989,12 +5999,12 @@
       <c r="BN28" s="78"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="164"/>
+      <c r="A29" s="166"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="161"/>
-      <c r="D29" s="162"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="158"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="201"/>
+      <c r="E29" s="190"/>
+      <c r="F29" s="197"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -6057,18 +6067,18 @@
       <c r="BN29" s="78"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="163">
+      <c r="A30" s="158">
         <v>12</v>
       </c>
       <c r="B30" s="36"/>
-      <c r="C30" s="159" t="s">
+      <c r="C30" s="198" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="160"/>
-      <c r="E30" s="155" t="s">
+      <c r="D30" s="199"/>
+      <c r="E30" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="157"/>
+      <c r="F30" s="196"/>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -6131,12 +6141,12 @@
       <c r="BN30" s="78"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="164"/>
+      <c r="A31" s="166"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="161"/>
-      <c r="D31" s="162"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="158"/>
+      <c r="C31" s="200"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="190"/>
+      <c r="F31" s="197"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -6186,8 +6196,8 @@
       <c r="BA31" s="154"/>
       <c r="BB31" s="13"/>
       <c r="BC31" s="19"/>
-      <c r="BD31" s="63"/>
-      <c r="BE31" s="63"/>
+      <c r="BD31" s="154"/>
+      <c r="BE31" s="154"/>
       <c r="BF31" s="63"/>
       <c r="BG31" s="63"/>
       <c r="BH31" s="63"/>
@@ -6199,18 +6209,18 @@
       <c r="BN31" s="78"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="163">
+      <c r="A32" s="158">
         <v>13</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="159" t="s">
+      <c r="C32" s="198" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="160"/>
-      <c r="E32" s="155" t="s">
+      <c r="D32" s="199"/>
+      <c r="E32" s="195" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="157"/>
+      <c r="F32" s="196"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -6273,12 +6283,12 @@
       <c r="BN32" s="78"/>
     </row>
     <row r="33" spans="1:66" ht="12" customHeight="1">
-      <c r="A33" s="164"/>
+      <c r="A33" s="166"/>
       <c r="B33" s="36"/>
-      <c r="C33" s="161"/>
-      <c r="D33" s="162"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="158"/>
+      <c r="C33" s="200"/>
+      <c r="D33" s="201"/>
+      <c r="E33" s="190"/>
+      <c r="F33" s="197"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -6341,18 +6351,18 @@
       <c r="BN33" s="78"/>
     </row>
     <row r="34" spans="1:66" ht="12" customHeight="1">
-      <c r="A34" s="163">
+      <c r="A34" s="158">
         <v>14</v>
       </c>
       <c r="B34" s="36"/>
-      <c r="C34" s="244" t="s">
+      <c r="C34" s="173" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="168"/>
-      <c r="E34" s="241" t="s">
+      <c r="D34" s="174"/>
+      <c r="E34" s="193" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="236"/>
+      <c r="F34" s="194"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -6415,12 +6425,12 @@
       <c r="BN34" s="78"/>
     </row>
     <row r="35" spans="1:66" ht="12" customHeight="1">
-      <c r="A35" s="164"/>
+      <c r="A35" s="166"/>
       <c r="B35" s="36"/>
-      <c r="C35" s="178"/>
-      <c r="D35" s="179"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="214"/>
+      <c r="C35" s="188"/>
+      <c r="D35" s="172"/>
+      <c r="E35" s="190"/>
+      <c r="F35" s="192"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -6483,20 +6493,20 @@
       <c r="BN35" s="78"/>
     </row>
     <row r="36" spans="1:66" ht="12" customHeight="1">
-      <c r="A36" s="163">
+      <c r="A36" s="158">
         <v>15</v>
       </c>
       <c r="B36" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="255" t="s">
+      <c r="C36" s="160" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="256"/>
-      <c r="E36" s="253" t="s">
+      <c r="D36" s="161"/>
+      <c r="E36" s="156" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="259"/>
+      <c r="F36" s="164"/>
       <c r="G36" s="38"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -6559,12 +6569,12 @@
       <c r="BN36" s="77"/>
     </row>
     <row r="37" spans="1:66" ht="12" customHeight="1">
-      <c r="A37" s="207"/>
+      <c r="A37" s="159"/>
       <c r="B37" s="34"/>
-      <c r="C37" s="257"/>
-      <c r="D37" s="258"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="260"/>
+      <c r="C37" s="162"/>
+      <c r="D37" s="163"/>
+      <c r="E37" s="157"/>
+      <c r="F37" s="165"/>
       <c r="G37" s="51"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
@@ -6614,11 +6624,11 @@
       <c r="BA37" s="63"/>
       <c r="BB37" s="13"/>
       <c r="BC37" s="19"/>
-      <c r="BD37" s="63"/>
+      <c r="BD37" s="155"/>
       <c r="BE37" s="63"/>
-      <c r="BF37" s="63"/>
-      <c r="BG37" s="63"/>
-      <c r="BH37" s="63"/>
+      <c r="BF37" s="154"/>
+      <c r="BG37" s="154"/>
+      <c r="BH37" s="154"/>
       <c r="BI37" s="13"/>
       <c r="BJ37" s="19"/>
       <c r="BK37" s="63"/>
@@ -6627,16 +6637,16 @@
       <c r="BN37" s="78"/>
     </row>
     <row r="38" spans="1:66" ht="12" customHeight="1">
-      <c r="A38" s="207"/>
+      <c r="A38" s="159"/>
       <c r="B38" s="34"/>
-      <c r="C38" s="264" t="s">
+      <c r="C38" s="171" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="179"/>
-      <c r="E38" s="261" t="s">
+      <c r="D38" s="172"/>
+      <c r="E38" s="167" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="262"/>
+      <c r="F38" s="169"/>
       <c r="G38" s="50"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -6699,12 +6709,12 @@
       <c r="BN38" s="104"/>
     </row>
     <row r="39" spans="1:66" ht="12" customHeight="1">
-      <c r="A39" s="164"/>
+      <c r="A39" s="166"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="257"/>
-      <c r="D39" s="258"/>
-      <c r="E39" s="246"/>
-      <c r="F39" s="263"/>
+      <c r="C39" s="162"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="168"/>
+      <c r="F39" s="170"/>
       <c r="G39" s="54"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -6767,17 +6777,17 @@
       <c r="BN39" s="76"/>
     </row>
     <row r="40" spans="1:66" ht="12" customHeight="1">
-      <c r="A40" s="163">
+      <c r="A40" s="158">
         <v>16</v>
       </c>
-      <c r="B40" s="249" t="s">
+      <c r="B40" s="180" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="238" t="s">
+      <c r="C40" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="239"/>
-      <c r="E40" s="245" t="s">
+      <c r="D40" s="185"/>
+      <c r="E40" s="177" t="s">
         <v>46</v>
       </c>
       <c r="F40" s="106"/>
@@ -6843,11 +6853,11 @@
       <c r="BN40" s="104"/>
     </row>
     <row r="41" spans="1:66" ht="12" customHeight="1">
-      <c r="A41" s="207"/>
-      <c r="B41" s="250"/>
-      <c r="C41" s="234"/>
-      <c r="D41" s="235"/>
-      <c r="E41" s="252"/>
+      <c r="A41" s="159"/>
+      <c r="B41" s="181"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="183"/>
       <c r="F41" s="106"/>
       <c r="G41" s="51"/>
       <c r="H41" s="7"/>
@@ -6902,7 +6912,7 @@
       <c r="BE41" s="63"/>
       <c r="BF41" s="63"/>
       <c r="BG41" s="63"/>
-      <c r="BH41" s="63"/>
+      <c r="BH41" s="154"/>
       <c r="BI41" s="13"/>
       <c r="BJ41" s="19"/>
       <c r="BK41" s="63"/>
@@ -6911,16 +6921,16 @@
       <c r="BN41" s="78"/>
     </row>
     <row r="42" spans="1:66" ht="12" customHeight="1">
-      <c r="A42" s="207"/>
-      <c r="B42" s="250"/>
-      <c r="C42" s="244" t="s">
+      <c r="A42" s="159"/>
+      <c r="B42" s="181"/>
+      <c r="C42" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="168"/>
-      <c r="E42" s="245" t="s">
+      <c r="D42" s="174"/>
+      <c r="E42" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="247"/>
+      <c r="F42" s="178"/>
       <c r="G42" s="50"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -6983,12 +6993,12 @@
       <c r="BN42" s="104"/>
     </row>
     <row r="43" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A43" s="164"/>
-      <c r="B43" s="251"/>
-      <c r="C43" s="169"/>
-      <c r="D43" s="170"/>
-      <c r="E43" s="246"/>
-      <c r="F43" s="248"/>
+      <c r="A43" s="166"/>
+      <c r="B43" s="182"/>
+      <c r="C43" s="175"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="168"/>
+      <c r="F43" s="179"/>
       <c r="G43" s="39"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -7074,22 +7084,61 @@
     </row>
   </sheetData>
   <mergeCells count="87">
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="C42:D43"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="C24:D25"/>
     <mergeCell ref="E24:E25"/>
@@ -7106,61 +7155,22 @@
     <mergeCell ref="E30:E31"/>
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="C30:D31"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="C38:D39"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
@@ -7196,54 +7206,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="235" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="238" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="193" t="s">
+      <c r="C1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="199" t="s">
+      <c r="D1" s="242"/>
+      <c r="E1" s="247" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="202" t="s">
+      <c r="F1" s="250" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="184"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="185"/>
-      <c r="P1" s="185"/>
-      <c r="Q1" s="185"/>
-      <c r="R1" s="185"/>
-      <c r="S1" s="185"/>
-      <c r="T1" s="185"/>
-      <c r="U1" s="185"/>
-      <c r="V1" s="185"/>
-      <c r="W1" s="185"/>
-      <c r="X1" s="185"/>
-      <c r="Y1" s="185"/>
-      <c r="Z1" s="185"/>
-      <c r="AA1" s="185"/>
-      <c r="AB1" s="185"/>
-      <c r="AC1" s="185"/>
-      <c r="AD1" s="186"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
+      <c r="S1" s="233"/>
+      <c r="T1" s="233"/>
+      <c r="U1" s="233"/>
+      <c r="V1" s="233"/>
+      <c r="W1" s="233"/>
+      <c r="X1" s="233"/>
+      <c r="Y1" s="233"/>
+      <c r="Z1" s="233"/>
+      <c r="AA1" s="233"/>
+      <c r="AB1" s="233"/>
+      <c r="AC1" s="233"/>
+      <c r="AD1" s="234"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="188"/>
-      <c r="B2" s="191"/>
-      <c r="C2" s="195"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="203"/>
+      <c r="A2" s="236"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="243"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="248"/>
+      <c r="F2" s="251"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -7318,12 +7328,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="189"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="201"/>
-      <c r="F3" s="204"/>
+      <c r="A3" s="237"/>
+      <c r="B3" s="240"/>
+      <c r="C3" s="245"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="249"/>
+      <c r="F3" s="252"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -7398,20 +7408,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="175">
+      <c r="A4" s="259">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="176" t="s">
+      <c r="C4" s="260" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="177"/>
-      <c r="E4" s="294" t="s">
+      <c r="D4" s="261"/>
+      <c r="E4" s="273" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="296"/>
+      <c r="F4" s="275"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -7434,20 +7444,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="298" t="s">
+      <c r="AC4" s="277" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="287" t="s">
+      <c r="AD4" s="266" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="166"/>
+      <c r="A5" s="254"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="295"/>
-      <c r="F5" s="297"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="274"/>
+      <c r="F5" s="276"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -7470,22 +7480,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="299"/>
-      <c r="AD5" s="288"/>
+      <c r="AC5" s="278"/>
+      <c r="AD5" s="267"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="165">
+      <c r="A6" s="253">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="167" t="s">
+      <c r="C6" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="168"/>
-      <c r="E6" s="290" t="s">
+      <c r="D6" s="174"/>
+      <c r="E6" s="269" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="292"/>
+      <c r="F6" s="271"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7508,16 +7518,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="299"/>
-      <c r="AD6" s="288"/>
+      <c r="AC6" s="278"/>
+      <c r="AD6" s="267"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="166"/>
+      <c r="A7" s="254"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="170"/>
-      <c r="E7" s="291"/>
-      <c r="F7" s="293"/>
+      <c r="C7" s="175"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="272"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7540,21 +7550,21 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="299"/>
-      <c r="AD7" s="288"/>
+      <c r="AC7" s="278"/>
+      <c r="AD7" s="267"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="163">
+      <c r="A8" s="158">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="208" t="s">
+      <c r="C8" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="209"/>
-      <c r="E8" s="302" t="s">
+      <c r="D8" s="210"/>
+      <c r="E8" s="281" t="s">
         <v>35</v>
       </c>
       <c r="F8" s="283"/>
@@ -7580,16 +7590,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="299"/>
-      <c r="AD8" s="288"/>
+      <c r="AC8" s="278"/>
+      <c r="AD8" s="267"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="164"/>
+      <c r="A9" s="166"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="219"/>
-      <c r="D9" s="301"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="280"/>
+      <c r="C9" s="217"/>
+      <c r="D9" s="280"/>
+      <c r="E9" s="282"/>
+      <c r="F9" s="284"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7612,24 +7622,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="299"/>
-      <c r="AD9" s="288"/>
+      <c r="AC9" s="278"/>
+      <c r="AD9" s="267"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="207">
+      <c r="A10" s="159">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="230" t="s">
+      <c r="C10" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="231"/>
-      <c r="E10" s="284" t="s">
+      <c r="D10" s="229"/>
+      <c r="E10" s="285" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="285"/>
+      <c r="F10" s="287"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7652,16 +7662,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="299"/>
-      <c r="AD10" s="288"/>
+      <c r="AC10" s="278"/>
+      <c r="AD10" s="267"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="164"/>
+      <c r="A11" s="166"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="210"/>
-      <c r="D11" s="211"/>
-      <c r="E11" s="277"/>
-      <c r="F11" s="279"/>
+      <c r="C11" s="211"/>
+      <c r="D11" s="212"/>
+      <c r="E11" s="286"/>
+      <c r="F11" s="288"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7684,22 +7694,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="299"/>
-      <c r="AD11" s="288"/>
+      <c r="AC11" s="278"/>
+      <c r="AD11" s="267"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="163">
+      <c r="A12" s="158">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="167" t="s">
+      <c r="C12" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="168"/>
-      <c r="E12" s="286" t="s">
+      <c r="D12" s="174"/>
+      <c r="E12" s="289" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="278"/>
+      <c r="F12" s="290"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7722,16 +7732,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="299"/>
-      <c r="AD12" s="288"/>
+      <c r="AC12" s="278"/>
+      <c r="AD12" s="267"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="207"/>
+      <c r="A13" s="159"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="234"/>
-      <c r="D13" s="235"/>
-      <c r="E13" s="284"/>
-      <c r="F13" s="285"/>
+      <c r="C13" s="186"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="285"/>
+      <c r="F13" s="287"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7754,21 +7764,21 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="299"/>
-      <c r="AD13" s="288"/>
+      <c r="AC13" s="278"/>
+      <c r="AD13" s="267"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="237">
+      <c r="A14" s="202">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="238" t="s">
+      <c r="C14" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="239"/>
-      <c r="E14" s="282" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="291" t="s">
         <v>38</v>
       </c>
       <c r="F14" s="283"/>
@@ -7794,16 +7804,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="299"/>
-      <c r="AD14" s="288"/>
+      <c r="AC14" s="278"/>
+      <c r="AD14" s="267"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="237"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="179"/>
-      <c r="E15" s="277"/>
-      <c r="F15" s="279"/>
+      <c r="C15" s="188"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="288"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7826,22 +7836,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="299"/>
-      <c r="AD15" s="288"/>
+      <c r="AC15" s="278"/>
+      <c r="AD15" s="267"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="237">
+      <c r="A16" s="202">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="203" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="168"/>
-      <c r="E16" s="276" t="s">
+      <c r="D16" s="174"/>
+      <c r="E16" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="278"/>
+      <c r="F16" s="290"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7864,16 +7874,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="299"/>
-      <c r="AD16" s="288"/>
+      <c r="AC16" s="278"/>
+      <c r="AD16" s="267"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="237"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="178"/>
-      <c r="D17" s="179"/>
-      <c r="E17" s="277"/>
-      <c r="F17" s="279"/>
+      <c r="C17" s="188"/>
+      <c r="D17" s="172"/>
+      <c r="E17" s="286"/>
+      <c r="F17" s="288"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7896,22 +7906,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="299"/>
-      <c r="AD17" s="288"/>
+      <c r="AC17" s="278"/>
+      <c r="AD17" s="267"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="237">
+      <c r="A18" s="202">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="167" t="s">
+      <c r="C18" s="203" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="168"/>
-      <c r="E18" s="276" t="s">
+      <c r="D18" s="174"/>
+      <c r="E18" s="292" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="278"/>
+      <c r="F18" s="290"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7934,16 +7944,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="299"/>
-      <c r="AD18" s="288"/>
+      <c r="AC18" s="278"/>
+      <c r="AD18" s="267"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="237"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="281"/>
-      <c r="F19" s="280"/>
+      <c r="C19" s="175"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="282"/>
+      <c r="F19" s="284"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7966,21 +7976,21 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="299"/>
-      <c r="AD19" s="288"/>
+      <c r="AC19" s="278"/>
+      <c r="AD19" s="267"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="163">
+      <c r="A20" s="158">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="238" t="s">
+      <c r="C20" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="239"/>
-      <c r="E20" s="282" t="s">
+      <c r="D20" s="185"/>
+      <c r="E20" s="291" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="283"/>
@@ -8006,18 +8016,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="299"/>
-      <c r="AD20" s="288"/>
+      <c r="AC20" s="278"/>
+      <c r="AD20" s="267"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="164"/>
+      <c r="A21" s="166"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="178"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="277"/>
-      <c r="F21" s="279"/>
+      <c r="C21" s="188"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="286"/>
+      <c r="F21" s="288"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -8040,22 +8050,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="299"/>
-      <c r="AD21" s="288"/>
+      <c r="AC21" s="278"/>
+      <c r="AD21" s="267"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="163">
+      <c r="A22" s="158">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="168"/>
-      <c r="E22" s="276" t="s">
+      <c r="D22" s="174"/>
+      <c r="E22" s="292" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="278"/>
+      <c r="F22" s="290"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -8078,16 +8088,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="299"/>
-      <c r="AD22" s="288"/>
+      <c r="AC22" s="278"/>
+      <c r="AD22" s="267"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="164"/>
+      <c r="A23" s="166"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="277"/>
-      <c r="F23" s="279"/>
+      <c r="C23" s="188"/>
+      <c r="D23" s="172"/>
+      <c r="E23" s="286"/>
+      <c r="F23" s="288"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -8110,22 +8120,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="299"/>
-      <c r="AD23" s="288"/>
+      <c r="AC23" s="278"/>
+      <c r="AD23" s="267"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="163">
+      <c r="A24" s="158">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="244" t="s">
+      <c r="C24" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="168"/>
-      <c r="E24" s="276" t="s">
+      <c r="D24" s="174"/>
+      <c r="E24" s="292" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="278"/>
+      <c r="F24" s="290"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -8148,16 +8158,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="299"/>
-      <c r="AD24" s="288"/>
+      <c r="AC24" s="278"/>
+      <c r="AD24" s="267"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="164"/>
+      <c r="A25" s="166"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="178"/>
-      <c r="D25" s="179"/>
-      <c r="E25" s="277"/>
-      <c r="F25" s="280"/>
+      <c r="C25" s="188"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="286"/>
+      <c r="F25" s="284"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -8180,24 +8190,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="299"/>
-      <c r="AD25" s="288"/>
+      <c r="AC25" s="278"/>
+      <c r="AD25" s="267"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="165">
+      <c r="A26" s="253">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="255" t="s">
+      <c r="C26" s="160" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="256"/>
-      <c r="E26" s="265" t="s">
+      <c r="D26" s="161"/>
+      <c r="E26" s="293" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="267"/>
+      <c r="F26" s="295"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -8220,16 +8230,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="299"/>
-      <c r="AD26" s="288"/>
+      <c r="AC26" s="278"/>
+      <c r="AD26" s="267"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="166"/>
+      <c r="A27" s="254"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="257"/>
-      <c r="D27" s="258"/>
-      <c r="E27" s="266"/>
-      <c r="F27" s="268"/>
+      <c r="C27" s="162"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="294"/>
+      <c r="F27" s="296"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -8252,24 +8262,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="299"/>
-      <c r="AD27" s="288"/>
+      <c r="AC27" s="278"/>
+      <c r="AD27" s="267"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="165">
+      <c r="A28" s="253">
         <v>14</v>
       </c>
-      <c r="B28" s="270" t="s">
+      <c r="B28" s="298" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="238" t="s">
+      <c r="C28" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="239"/>
-      <c r="E28" s="270" t="s">
+      <c r="D28" s="185"/>
+      <c r="E28" s="298" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="274"/>
+      <c r="F28" s="302"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -8292,16 +8302,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="299"/>
-      <c r="AD28" s="288"/>
+      <c r="AC28" s="278"/>
+      <c r="AD28" s="267"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="269"/>
-      <c r="B29" s="271"/>
-      <c r="C29" s="272"/>
-      <c r="D29" s="273"/>
-      <c r="E29" s="271"/>
-      <c r="F29" s="275"/>
+      <c r="A29" s="297"/>
+      <c r="B29" s="299"/>
+      <c r="C29" s="300"/>
+      <c r="D29" s="301"/>
+      <c r="E29" s="299"/>
+      <c r="F29" s="303"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -8324,8 +8334,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="300"/>
-      <c r="AD29" s="289"/>
+      <c r="AC29" s="279"/>
+      <c r="AD29" s="268"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
@@ -8345,12 +8355,45 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G1:AD1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="AD4:AD29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D7"/>
@@ -8367,45 +8410,12 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G1:AD1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/000-要件定義/003-WBS.xlsx
+++ b/000-要件定義/003-WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\000-要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214245D6-B711-4BA9-9BBA-752BE08F08DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA49D463-8A19-448F-BC8F-74D5AB12E7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体スケジュール (テンプレート)" sheetId="13" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="61">
   <si>
     <t>進捗</t>
     <rPh sb="0" eb="2">
@@ -570,6 +570,10 @@
       <t>コウニュウキノウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>100%</t>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>100%</t>
@@ -704,7 +708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="109">
+  <borders count="110">
     <border>
       <left/>
       <right/>
@@ -2052,11 +2056,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2365,599 +2382,584 @@
     <xf numFmtId="49" fontId="2" fillId="10" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="107" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="107" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="109" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="93" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3662,108 +3664,108 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BN47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="102" customWidth="1"/>
-    <col min="7" max="30" width="3.109375" style="3" customWidth="1"/>
-    <col min="31" max="66" width="3.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" style="102" customWidth="1"/>
+    <col min="7" max="30" width="3.125" style="3" customWidth="1"/>
+    <col min="31" max="66" width="3.125" style="1" customWidth="1"/>
     <col min="67" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="238" t="s">
+      <c r="B1" s="227" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="241" t="s">
+      <c r="C1" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="242"/>
-      <c r="E1" s="247" t="s">
+      <c r="D1" s="231"/>
+      <c r="E1" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="250" t="s">
+      <c r="F1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="232">
+      <c r="G1" s="221">
         <v>45536</v>
       </c>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="233"/>
-      <c r="U1" s="233"/>
-      <c r="V1" s="233"/>
-      <c r="W1" s="233"/>
-      <c r="X1" s="233"/>
-      <c r="Y1" s="233"/>
-      <c r="Z1" s="233"/>
-      <c r="AA1" s="233"/>
-      <c r="AB1" s="233"/>
-      <c r="AC1" s="233"/>
-      <c r="AD1" s="233"/>
-      <c r="AE1" s="233"/>
-      <c r="AF1" s="233"/>
-      <c r="AG1" s="233"/>
-      <c r="AH1" s="233"/>
-      <c r="AI1" s="233"/>
-      <c r="AJ1" s="234"/>
-      <c r="AK1" s="232">
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="222"/>
+      <c r="S1" s="222"/>
+      <c r="T1" s="222"/>
+      <c r="U1" s="222"/>
+      <c r="V1" s="222"/>
+      <c r="W1" s="222"/>
+      <c r="X1" s="222"/>
+      <c r="Y1" s="222"/>
+      <c r="Z1" s="222"/>
+      <c r="AA1" s="222"/>
+      <c r="AB1" s="222"/>
+      <c r="AC1" s="222"/>
+      <c r="AD1" s="222"/>
+      <c r="AE1" s="222"/>
+      <c r="AF1" s="222"/>
+      <c r="AG1" s="222"/>
+      <c r="AH1" s="222"/>
+      <c r="AI1" s="222"/>
+      <c r="AJ1" s="223"/>
+      <c r="AK1" s="221">
         <v>45566</v>
       </c>
-      <c r="AL1" s="233"/>
-      <c r="AM1" s="233"/>
-      <c r="AN1" s="233"/>
-      <c r="AO1" s="233"/>
-      <c r="AP1" s="233"/>
-      <c r="AQ1" s="233"/>
-      <c r="AR1" s="233"/>
-      <c r="AS1" s="233"/>
-      <c r="AT1" s="233"/>
-      <c r="AU1" s="233"/>
-      <c r="AV1" s="233"/>
-      <c r="AW1" s="233"/>
-      <c r="AX1" s="233"/>
-      <c r="AY1" s="233"/>
-      <c r="AZ1" s="233"/>
-      <c r="BA1" s="233"/>
-      <c r="BB1" s="233"/>
-      <c r="BC1" s="233"/>
-      <c r="BD1" s="233"/>
-      <c r="BE1" s="233"/>
-      <c r="BF1" s="233"/>
-      <c r="BG1" s="233"/>
-      <c r="BH1" s="233"/>
-      <c r="BI1" s="233"/>
-      <c r="BJ1" s="233"/>
-      <c r="BK1" s="233"/>
-      <c r="BL1" s="233"/>
-      <c r="BM1" s="233"/>
-      <c r="BN1" s="234"/>
+      <c r="AL1" s="222"/>
+      <c r="AM1" s="222"/>
+      <c r="AN1" s="222"/>
+      <c r="AO1" s="222"/>
+      <c r="AP1" s="222"/>
+      <c r="AQ1" s="222"/>
+      <c r="AR1" s="222"/>
+      <c r="AS1" s="222"/>
+      <c r="AT1" s="222"/>
+      <c r="AU1" s="222"/>
+      <c r="AV1" s="222"/>
+      <c r="AW1" s="222"/>
+      <c r="AX1" s="222"/>
+      <c r="AY1" s="222"/>
+      <c r="AZ1" s="222"/>
+      <c r="BA1" s="222"/>
+      <c r="BB1" s="222"/>
+      <c r="BC1" s="222"/>
+      <c r="BD1" s="222"/>
+      <c r="BE1" s="222"/>
+      <c r="BF1" s="222"/>
+      <c r="BG1" s="222"/>
+      <c r="BH1" s="222"/>
+      <c r="BI1" s="222"/>
+      <c r="BJ1" s="222"/>
+      <c r="BK1" s="222"/>
+      <c r="BL1" s="222"/>
+      <c r="BM1" s="222"/>
+      <c r="BN1" s="223"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="236"/>
-      <c r="B2" s="239"/>
-      <c r="C2" s="243"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="251"/>
+      <c r="A2" s="225"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="46">
         <v>45537</v>
       </c>
@@ -4005,12 +4007,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="237"/>
-      <c r="B3" s="240"/>
-      <c r="C3" s="245"/>
-      <c r="D3" s="246"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="252"/>
+      <c r="A3" s="226"/>
+      <c r="B3" s="229"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="241"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -4193,20 +4195,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="259">
+      <c r="A4" s="246">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="261"/>
-      <c r="E4" s="262" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="249" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="264" t="s">
+      <c r="F4" s="292" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="93"/>
@@ -4271,12 +4273,12 @@
       <c r="BN4" s="69"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="254"/>
+      <c r="A5" s="243"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="263"/>
-      <c r="F5" s="265"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="293"/>
       <c r="G5" s="95"/>
       <c r="H5" s="62"/>
       <c r="I5" s="62"/>
@@ -4339,18 +4341,18 @@
       <c r="BN5" s="70"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="253">
+      <c r="A6" s="242">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="203" t="s">
+      <c r="C6" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="174"/>
-      <c r="E6" s="255" t="s">
+      <c r="D6" s="171"/>
+      <c r="E6" s="244" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="257" t="s">
+      <c r="F6" s="166" t="s">
         <v>45</v>
       </c>
       <c r="G6" s="51"/>
@@ -4415,12 +4417,12 @@
       <c r="BN6" s="71"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="254"/>
+      <c r="A7" s="243"/>
       <c r="B7" s="96"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="256"/>
-      <c r="F7" s="258"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="289"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
@@ -4483,20 +4485,20 @@
       <c r="BN7" s="72"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="159">
+      <c r="A8" s="158">
         <v>3</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="209" t="s">
+      <c r="C8" s="198" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="210"/>
-      <c r="E8" s="230" t="s">
+      <c r="D8" s="199"/>
+      <c r="E8" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="191" t="s">
+      <c r="F8" s="294" t="s">
         <v>58</v>
       </c>
       <c r="G8" s="38"/>
@@ -4560,238 +4562,238 @@
       <c r="BM8" s="6"/>
       <c r="BN8" s="73"/>
     </row>
-    <row r="9" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A9" s="166"/>
-      <c r="B9" s="107"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="231"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="113"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="146"/>
-      <c r="O9" s="146"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="146"/>
-      <c r="R9" s="146"/>
-      <c r="S9" s="115"/>
-      <c r="T9" s="116"/>
-      <c r="U9" s="116"/>
-      <c r="V9" s="146"/>
-      <c r="W9" s="114"/>
-      <c r="X9" s="117"/>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="116"/>
-      <c r="AB9" s="116"/>
-      <c r="AC9" s="146"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117"/>
-      <c r="AG9" s="115"/>
-      <c r="AH9" s="116"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="118"/>
-      <c r="AK9" s="119"/>
-      <c r="AL9" s="117"/>
-      <c r="AM9" s="117"/>
-      <c r="AN9" s="115"/>
-      <c r="AO9" s="116"/>
-      <c r="AP9" s="117"/>
-      <c r="AQ9" s="117"/>
-      <c r="AR9" s="117"/>
-      <c r="AS9" s="117"/>
-      <c r="AT9" s="117"/>
-      <c r="AU9" s="115"/>
-      <c r="AV9" s="116"/>
-      <c r="AW9" s="116"/>
-      <c r="AX9" s="117"/>
-      <c r="AY9" s="117"/>
-      <c r="AZ9" s="117"/>
-      <c r="BA9" s="117"/>
-      <c r="BB9" s="115"/>
-      <c r="BC9" s="116"/>
-      <c r="BD9" s="117"/>
-      <c r="BE9" s="117"/>
-      <c r="BF9" s="117"/>
-      <c r="BG9" s="117"/>
-      <c r="BH9" s="117"/>
-      <c r="BI9" s="115"/>
-      <c r="BJ9" s="116"/>
-      <c r="BK9" s="117"/>
-      <c r="BL9" s="117"/>
-      <c r="BM9" s="117"/>
-      <c r="BN9" s="118"/>
+    <row r="9" spans="1:66" ht="13.15" customHeight="1">
+      <c r="A9" s="163"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="217"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="220"/>
+      <c r="F9" s="213"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="114"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="145"/>
+      <c r="O9" s="145"/>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="114"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
+      <c r="V9" s="145"/>
+      <c r="W9" s="113"/>
+      <c r="X9" s="116"/>
+      <c r="Y9" s="116"/>
+      <c r="Z9" s="114"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="145"/>
+      <c r="AD9" s="116"/>
+      <c r="AE9" s="116"/>
+      <c r="AF9" s="116"/>
+      <c r="AG9" s="114"/>
+      <c r="AH9" s="115"/>
+      <c r="AI9" s="116"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="116"/>
+      <c r="AM9" s="116"/>
+      <c r="AN9" s="114"/>
+      <c r="AO9" s="115"/>
+      <c r="AP9" s="116"/>
+      <c r="AQ9" s="116"/>
+      <c r="AR9" s="116"/>
+      <c r="AS9" s="116"/>
+      <c r="AT9" s="116"/>
+      <c r="AU9" s="114"/>
+      <c r="AV9" s="115"/>
+      <c r="AW9" s="115"/>
+      <c r="AX9" s="116"/>
+      <c r="AY9" s="116"/>
+      <c r="AZ9" s="116"/>
+      <c r="BA9" s="116"/>
+      <c r="BB9" s="114"/>
+      <c r="BC9" s="115"/>
+      <c r="BD9" s="116"/>
+      <c r="BE9" s="116"/>
+      <c r="BF9" s="116"/>
+      <c r="BG9" s="116"/>
+      <c r="BH9" s="116"/>
+      <c r="BI9" s="114"/>
+      <c r="BJ9" s="115"/>
+      <c r="BK9" s="116"/>
+      <c r="BL9" s="116"/>
+      <c r="BM9" s="116"/>
+      <c r="BN9" s="117"/>
     </row>
-    <row r="10" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A10" s="213"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="215" t="s">
+    <row r="10" spans="1:66" ht="13.15" customHeight="1">
+      <c r="A10" s="202"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="204" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="225"/>
-      <c r="E10" s="221" t="s">
+      <c r="D10" s="214"/>
+      <c r="E10" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="222" t="s">
+      <c r="F10" s="211" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="133"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="135"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
-      <c r="S10" s="135"/>
-      <c r="T10" s="136"/>
-      <c r="U10" s="136"/>
-      <c r="V10" s="141"/>
-      <c r="W10" s="134"/>
-      <c r="X10" s="137"/>
-      <c r="Y10" s="137"/>
-      <c r="Z10" s="135"/>
-      <c r="AA10" s="136"/>
-      <c r="AB10" s="136"/>
-      <c r="AC10" s="137"/>
-      <c r="AD10" s="137"/>
-      <c r="AE10" s="137"/>
-      <c r="AF10" s="137"/>
-      <c r="AG10" s="135"/>
-      <c r="AH10" s="136"/>
-      <c r="AI10" s="137"/>
-      <c r="AJ10" s="138"/>
-      <c r="AK10" s="139"/>
-      <c r="AL10" s="137"/>
-      <c r="AM10" s="137"/>
-      <c r="AN10" s="135"/>
-      <c r="AO10" s="136"/>
-      <c r="AP10" s="137"/>
-      <c r="AQ10" s="137"/>
-      <c r="AR10" s="137"/>
-      <c r="AS10" s="137"/>
-      <c r="AT10" s="137"/>
-      <c r="AU10" s="135"/>
-      <c r="AV10" s="136"/>
-      <c r="AW10" s="136"/>
-      <c r="AX10" s="137"/>
-      <c r="AY10" s="137"/>
-      <c r="AZ10" s="137"/>
-      <c r="BA10" s="137"/>
-      <c r="BB10" s="135"/>
-      <c r="BC10" s="136"/>
-      <c r="BD10" s="137"/>
-      <c r="BE10" s="137"/>
-      <c r="BF10" s="137"/>
-      <c r="BG10" s="137"/>
-      <c r="BH10" s="137"/>
-      <c r="BI10" s="135"/>
-      <c r="BJ10" s="136"/>
-      <c r="BK10" s="137"/>
-      <c r="BL10" s="137"/>
-      <c r="BM10" s="137"/>
-      <c r="BN10" s="138"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="133"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="133"/>
+      <c r="R10" s="133"/>
+      <c r="S10" s="134"/>
+      <c r="T10" s="135"/>
+      <c r="U10" s="135"/>
+      <c r="V10" s="140"/>
+      <c r="W10" s="133"/>
+      <c r="X10" s="136"/>
+      <c r="Y10" s="136"/>
+      <c r="Z10" s="134"/>
+      <c r="AA10" s="135"/>
+      <c r="AB10" s="135"/>
+      <c r="AC10" s="136"/>
+      <c r="AD10" s="136"/>
+      <c r="AE10" s="136"/>
+      <c r="AF10" s="136"/>
+      <c r="AG10" s="134"/>
+      <c r="AH10" s="135"/>
+      <c r="AI10" s="136"/>
+      <c r="AJ10" s="137"/>
+      <c r="AK10" s="138"/>
+      <c r="AL10" s="136"/>
+      <c r="AM10" s="136"/>
+      <c r="AN10" s="134"/>
+      <c r="AO10" s="135"/>
+      <c r="AP10" s="136"/>
+      <c r="AQ10" s="136"/>
+      <c r="AR10" s="136"/>
+      <c r="AS10" s="136"/>
+      <c r="AT10" s="136"/>
+      <c r="AU10" s="134"/>
+      <c r="AV10" s="135"/>
+      <c r="AW10" s="135"/>
+      <c r="AX10" s="136"/>
+      <c r="AY10" s="136"/>
+      <c r="AZ10" s="136"/>
+      <c r="BA10" s="136"/>
+      <c r="BB10" s="134"/>
+      <c r="BC10" s="135"/>
+      <c r="BD10" s="136"/>
+      <c r="BE10" s="136"/>
+      <c r="BF10" s="136"/>
+      <c r="BG10" s="136"/>
+      <c r="BH10" s="136"/>
+      <c r="BI10" s="134"/>
+      <c r="BJ10" s="135"/>
+      <c r="BK10" s="136"/>
+      <c r="BL10" s="136"/>
+      <c r="BM10" s="136"/>
+      <c r="BN10" s="137"/>
     </row>
-    <row r="11" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A11" s="214"/>
-      <c r="B11" s="107"/>
-      <c r="C11" s="226"/>
-      <c r="D11" s="227"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="110"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="145"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="147"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="128"/>
-      <c r="U11" s="128"/>
-      <c r="V11" s="147"/>
-      <c r="W11" s="126"/>
-      <c r="X11" s="130"/>
-      <c r="Y11" s="130"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="128"/>
-      <c r="AB11" s="128"/>
-      <c r="AC11" s="130"/>
-      <c r="AD11" s="130"/>
-      <c r="AE11" s="130"/>
-      <c r="AF11" s="130"/>
-      <c r="AG11" s="127"/>
-      <c r="AH11" s="128"/>
-      <c r="AI11" s="130"/>
-      <c r="AJ11" s="131"/>
-      <c r="AK11" s="132"/>
-      <c r="AL11" s="130"/>
-      <c r="AM11" s="130"/>
-      <c r="AN11" s="127"/>
-      <c r="AO11" s="128"/>
-      <c r="AP11" s="130"/>
-      <c r="AQ11" s="130"/>
-      <c r="AR11" s="130"/>
-      <c r="AS11" s="130"/>
-      <c r="AT11" s="130"/>
-      <c r="AU11" s="127"/>
-      <c r="AV11" s="128"/>
-      <c r="AW11" s="128"/>
-      <c r="AX11" s="130"/>
-      <c r="AY11" s="130"/>
-      <c r="AZ11" s="130"/>
-      <c r="BA11" s="130"/>
-      <c r="BB11" s="127"/>
-      <c r="BC11" s="128"/>
-      <c r="BD11" s="130"/>
-      <c r="BE11" s="130"/>
-      <c r="BF11" s="130"/>
-      <c r="BG11" s="130"/>
-      <c r="BH11" s="130"/>
-      <c r="BI11" s="127"/>
-      <c r="BJ11" s="128"/>
-      <c r="BK11" s="130"/>
-      <c r="BL11" s="130"/>
-      <c r="BM11" s="130"/>
-      <c r="BN11" s="131"/>
+    <row r="11" spans="1:66" ht="13.15" customHeight="1">
+      <c r="A11" s="203"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="215"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="197"/>
+      <c r="F11" s="212"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="109"/>
+      <c r="M11" s="110"/>
+      <c r="N11" s="144"/>
+      <c r="O11" s="125"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="146"/>
+      <c r="S11" s="126"/>
+      <c r="T11" s="127"/>
+      <c r="U11" s="127"/>
+      <c r="V11" s="146"/>
+      <c r="W11" s="125"/>
+      <c r="X11" s="129"/>
+      <c r="Y11" s="129"/>
+      <c r="Z11" s="126"/>
+      <c r="AA11" s="127"/>
+      <c r="AB11" s="127"/>
+      <c r="AC11" s="129"/>
+      <c r="AD11" s="129"/>
+      <c r="AE11" s="129"/>
+      <c r="AF11" s="129"/>
+      <c r="AG11" s="126"/>
+      <c r="AH11" s="127"/>
+      <c r="AI11" s="129"/>
+      <c r="AJ11" s="130"/>
+      <c r="AK11" s="131"/>
+      <c r="AL11" s="129"/>
+      <c r="AM11" s="129"/>
+      <c r="AN11" s="126"/>
+      <c r="AO11" s="127"/>
+      <c r="AP11" s="129"/>
+      <c r="AQ11" s="129"/>
+      <c r="AR11" s="129"/>
+      <c r="AS11" s="129"/>
+      <c r="AT11" s="129"/>
+      <c r="AU11" s="126"/>
+      <c r="AV11" s="127"/>
+      <c r="AW11" s="127"/>
+      <c r="AX11" s="129"/>
+      <c r="AY11" s="129"/>
+      <c r="AZ11" s="129"/>
+      <c r="BA11" s="129"/>
+      <c r="BB11" s="126"/>
+      <c r="BC11" s="127"/>
+      <c r="BD11" s="129"/>
+      <c r="BE11" s="129"/>
+      <c r="BF11" s="129"/>
+      <c r="BG11" s="129"/>
+      <c r="BH11" s="129"/>
+      <c r="BI11" s="126"/>
+      <c r="BJ11" s="127"/>
+      <c r="BK11" s="129"/>
+      <c r="BL11" s="129"/>
+      <c r="BM11" s="129"/>
+      <c r="BN11" s="130"/>
     </row>
-    <row r="12" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A12" s="213"/>
+    <row r="12" spans="1:66" ht="13.15" customHeight="1">
+      <c r="A12" s="202"/>
       <c r="B12" s="36"/>
-      <c r="C12" s="215" t="s">
+      <c r="C12" s="204" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="216"/>
-      <c r="E12" s="219" t="s">
+      <c r="D12" s="205"/>
+      <c r="E12" s="208" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="222" t="s">
+      <c r="F12" s="211" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="120"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="123"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="129"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="128"/>
       <c r="P12" s="105"/>
       <c r="Q12" s="41"/>
       <c r="R12" s="41"/>
@@ -4844,36 +4846,36 @@
       <c r="BM12" s="9"/>
       <c r="BN12" s="70"/>
     </row>
-    <row r="13" spans="1:66" ht="13.2" customHeight="1">
-      <c r="A13" s="214"/>
+    <row r="13" spans="1:66" ht="13.15" customHeight="1">
+      <c r="A13" s="203"/>
       <c r="B13" s="37"/>
-      <c r="C13" s="217"/>
-      <c r="D13" s="218"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="224"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="126"/>
-      <c r="O13" s="148"/>
-      <c r="P13" s="149"/>
-      <c r="Q13" s="150"/>
-      <c r="R13" s="150"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="207"/>
+      <c r="E13" s="209"/>
+      <c r="F13" s="213"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="125"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="125"/>
+      <c r="O13" s="147"/>
+      <c r="P13" s="148"/>
+      <c r="Q13" s="149"/>
+      <c r="R13" s="149"/>
       <c r="S13" s="44"/>
       <c r="T13" s="45"/>
       <c r="U13" s="45"/>
-      <c r="V13" s="150"/>
-      <c r="W13" s="150"/>
+      <c r="V13" s="149"/>
+      <c r="W13" s="149"/>
       <c r="X13" s="43"/>
       <c r="Y13" s="43"/>
       <c r="Z13" s="44"/>
       <c r="AA13" s="45"/>
       <c r="AB13" s="45"/>
-      <c r="AC13" s="150"/>
+      <c r="AC13" s="149"/>
       <c r="AD13" s="43"/>
       <c r="AE13" s="43"/>
       <c r="AF13" s="43"/>
@@ -4913,20 +4915,20 @@
       <c r="BN13" s="74"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="159">
+      <c r="A14" s="158">
         <v>4</v>
       </c>
       <c r="B14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="209" t="s">
+      <c r="C14" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="210"/>
-      <c r="E14" s="206" t="s">
+      <c r="D14" s="199"/>
+      <c r="E14" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="207" t="s">
+      <c r="F14" s="212" t="s">
         <v>58</v>
       </c>
       <c r="G14" s="50"/>
@@ -4936,7 +4938,7 @@
       <c r="K14" s="62"/>
       <c r="L14" s="16"/>
       <c r="M14" s="22"/>
-      <c r="N14" s="112"/>
+      <c r="N14" s="111"/>
       <c r="O14" s="62"/>
       <c r="P14" s="62"/>
       <c r="Q14" s="62"/>
@@ -4944,7 +4946,7 @@
       <c r="S14" s="16"/>
       <c r="T14" s="22"/>
       <c r="U14" s="22"/>
-      <c r="V14" s="142"/>
+      <c r="V14" s="141"/>
       <c r="W14" s="41"/>
       <c r="X14" s="41"/>
       <c r="Y14" s="41"/>
@@ -4991,12 +4993,12 @@
       <c r="BN14" s="70"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="166"/>
+      <c r="A15" s="163"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="190"/>
-      <c r="F15" s="192"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="185"/>
+      <c r="F15" s="189"/>
       <c r="G15" s="50"/>
       <c r="H15" s="62"/>
       <c r="I15" s="62"/>
@@ -5059,18 +5061,18 @@
       <c r="BN15" s="70"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="158">
+      <c r="A16" s="157">
         <v>5</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="203" t="s">
+      <c r="C16" s="195" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="174"/>
-      <c r="E16" s="195" t="s">
+      <c r="D16" s="171"/>
+      <c r="E16" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="194" t="s">
+      <c r="F16" s="188" t="s">
         <v>45</v>
       </c>
       <c r="G16" s="51"/>
@@ -5135,12 +5137,12 @@
       <c r="BN16" s="71"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="159"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="187"/>
-      <c r="E17" s="206"/>
-      <c r="F17" s="207"/>
+      <c r="C17" s="181"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="197"/>
+      <c r="F17" s="212"/>
       <c r="G17" s="52"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
@@ -5170,8 +5172,8 @@
       <c r="AG17" s="25"/>
       <c r="AH17" s="26"/>
       <c r="AI17" s="24"/>
-      <c r="AJ17" s="151"/>
-      <c r="AK17" s="152"/>
+      <c r="AJ17" s="150"/>
+      <c r="AK17" s="151"/>
       <c r="AL17" s="24"/>
       <c r="AM17" s="24"/>
       <c r="AN17" s="25"/>
@@ -5203,20 +5205,20 @@
       <c r="BN17" s="72"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="202">
+      <c r="A18" s="194">
         <v>6</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="184" t="s">
+      <c r="C18" s="179" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="189" t="s">
+      <c r="D18" s="180"/>
+      <c r="E18" s="184" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="191" t="s">
+      <c r="F18" s="294" t="s">
         <v>59</v>
       </c>
       <c r="G18" s="38"/>
@@ -5281,12 +5283,12 @@
       <c r="BN18" s="73"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="202"/>
+      <c r="A19" s="194"/>
       <c r="B19" s="36"/>
-      <c r="C19" s="188"/>
-      <c r="D19" s="172"/>
-      <c r="E19" s="190"/>
-      <c r="F19" s="192"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="169"/>
+      <c r="E19" s="185"/>
+      <c r="F19" s="189"/>
       <c r="G19" s="52"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
@@ -5317,7 +5319,7 @@
       <c r="AH19" s="26"/>
       <c r="AI19" s="24"/>
       <c r="AJ19" s="72"/>
-      <c r="AK19" s="152"/>
+      <c r="AK19" s="151"/>
       <c r="AL19" s="32"/>
       <c r="AM19" s="32"/>
       <c r="AN19" s="25"/>
@@ -5349,18 +5351,18 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="202">
+      <c r="A20" s="194">
         <v>7</v>
       </c>
       <c r="B20" s="36"/>
-      <c r="C20" s="203" t="s">
+      <c r="C20" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="174"/>
-      <c r="E20" s="193" t="s">
+      <c r="D20" s="171"/>
+      <c r="E20" s="186" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="194" t="s">
+      <c r="F20" s="188" t="s">
         <v>59</v>
       </c>
       <c r="G20" s="51"/>
@@ -5425,12 +5427,12 @@
       <c r="BN20" s="71"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="202"/>
+      <c r="A21" s="194"/>
       <c r="B21" s="36"/>
-      <c r="C21" s="188"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="190"/>
-      <c r="F21" s="192"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="185"/>
+      <c r="F21" s="189"/>
       <c r="G21" s="52"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
@@ -5493,18 +5495,18 @@
       <c r="BN21" s="72"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="202">
+      <c r="A22" s="194">
         <v>8</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="203" t="s">
+      <c r="C22" s="195" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="174"/>
-      <c r="E22" s="193" t="s">
+      <c r="D22" s="171"/>
+      <c r="E22" s="186" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="194" t="s">
+      <c r="F22" s="188" t="s">
         <v>59</v>
       </c>
       <c r="G22" s="52"/>
@@ -5569,12 +5571,12 @@
       <c r="BN22" s="75"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="202"/>
+      <c r="A23" s="194"/>
       <c r="B23" s="37"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="204"/>
-      <c r="F23" s="205"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="196"/>
+      <c r="F23" s="295"/>
       <c r="G23" s="54"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
@@ -5610,11 +5612,11 @@
       <c r="AM23" s="66"/>
       <c r="AN23" s="17"/>
       <c r="AO23" s="23"/>
-      <c r="AP23" s="153"/>
+      <c r="AP23" s="152"/>
       <c r="AQ23" s="66"/>
-      <c r="AR23" s="153"/>
-      <c r="AS23" s="153"/>
-      <c r="AT23" s="153"/>
+      <c r="AR23" s="152"/>
+      <c r="AS23" s="152"/>
+      <c r="AT23" s="152"/>
       <c r="AU23" s="17"/>
       <c r="AV23" s="23"/>
       <c r="AW23" s="23"/>
@@ -5637,20 +5639,20 @@
       <c r="BN23" s="76"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="158">
+      <c r="A24" s="157">
         <v>9</v>
       </c>
       <c r="B24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="184" t="s">
+      <c r="C24" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="185"/>
-      <c r="E24" s="189" t="s">
+      <c r="D24" s="180"/>
+      <c r="E24" s="184" t="s">
         <v>46</v>
       </c>
-      <c r="F24" s="191"/>
+      <c r="F24" s="294"/>
       <c r="G24" s="38"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -5680,7 +5682,7 @@
       <c r="AG24" s="15"/>
       <c r="AH24" s="21"/>
       <c r="AI24" s="65"/>
-      <c r="AJ24" s="143"/>
+      <c r="AJ24" s="142"/>
       <c r="AK24" s="88"/>
       <c r="AL24" s="65"/>
       <c r="AM24" s="65"/>
@@ -5713,14 +5715,14 @@
       <c r="BN24" s="77"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="166"/>
+      <c r="A25" s="163"/>
       <c r="B25" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="188"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="190"/>
-      <c r="F25" s="192"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="185"/>
+      <c r="F25" s="189"/>
       <c r="G25" s="51"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -5760,7 +5762,7 @@
       <c r="AQ25" s="63"/>
       <c r="AR25" s="63"/>
       <c r="AS25" s="63"/>
-      <c r="AT25" s="154"/>
+      <c r="AT25" s="153"/>
       <c r="AU25" s="13"/>
       <c r="AV25" s="19"/>
       <c r="AW25" s="19"/>
@@ -5783,18 +5785,18 @@
       <c r="BN25" s="78"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="158">
+      <c r="A26" s="157">
         <v>10</v>
       </c>
       <c r="B26" s="36"/>
-      <c r="C26" s="198" t="s">
+      <c r="C26" s="190" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="199"/>
-      <c r="E26" s="195" t="s">
+      <c r="D26" s="191"/>
+      <c r="E26" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="196"/>
+      <c r="F26" s="188"/>
       <c r="G26" s="51"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -5825,7 +5827,7 @@
       <c r="AH26" s="19"/>
       <c r="AI26" s="63"/>
       <c r="AJ26" s="94"/>
-      <c r="AK26" s="144"/>
+      <c r="AK26" s="143"/>
       <c r="AL26" s="30"/>
       <c r="AM26" s="63"/>
       <c r="AN26" s="13"/>
@@ -5857,12 +5859,12 @@
       <c r="BN26" s="78"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="166"/>
+      <c r="A27" s="163"/>
       <c r="B27" s="36"/>
-      <c r="C27" s="200"/>
-      <c r="D27" s="201"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="197"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="193"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="189"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -5925,18 +5927,18 @@
       <c r="BN27" s="78"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="158">
+      <c r="A28" s="157">
         <v>11</v>
       </c>
       <c r="B28" s="36"/>
-      <c r="C28" s="198" t="s">
+      <c r="C28" s="190" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="199"/>
-      <c r="E28" s="195" t="s">
+      <c r="D28" s="191"/>
+      <c r="E28" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="196"/>
+      <c r="F28" s="188"/>
       <c r="G28" s="51"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -5999,12 +6001,12 @@
       <c r="BN28" s="78"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="166"/>
+      <c r="A29" s="163"/>
       <c r="B29" s="36"/>
-      <c r="C29" s="200"/>
-      <c r="D29" s="201"/>
-      <c r="E29" s="190"/>
-      <c r="F29" s="197"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="185"/>
+      <c r="F29" s="189"/>
       <c r="G29" s="51"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -6067,18 +6069,20 @@
       <c r="BN29" s="78"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="158">
+      <c r="A30" s="157">
         <v>12</v>
       </c>
       <c r="B30" s="36"/>
-      <c r="C30" s="198" t="s">
+      <c r="C30" s="190" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="199"/>
-      <c r="E30" s="195" t="s">
+      <c r="D30" s="191"/>
+      <c r="E30" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="196"/>
+      <c r="F30" s="188" t="s">
+        <v>60</v>
+      </c>
       <c r="G30" s="51"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -6141,12 +6145,12 @@
       <c r="BN30" s="78"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="166"/>
+      <c r="A31" s="163"/>
       <c r="B31" s="36"/>
-      <c r="C31" s="200"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="190"/>
-      <c r="F31" s="197"/>
+      <c r="C31" s="192"/>
+      <c r="D31" s="193"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="189"/>
       <c r="G31" s="51"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -6190,14 +6194,14 @@
       <c r="AU31" s="13"/>
       <c r="AV31" s="19"/>
       <c r="AW31" s="19"/>
-      <c r="AX31" s="154"/>
-      <c r="AY31" s="154"/>
-      <c r="AZ31" s="154"/>
-      <c r="BA31" s="154"/>
+      <c r="AX31" s="153"/>
+      <c r="AY31" s="153"/>
+      <c r="AZ31" s="153"/>
+      <c r="BA31" s="153"/>
       <c r="BB31" s="13"/>
       <c r="BC31" s="19"/>
-      <c r="BD31" s="154"/>
-      <c r="BE31" s="154"/>
+      <c r="BD31" s="153"/>
+      <c r="BE31" s="153"/>
       <c r="BF31" s="63"/>
       <c r="BG31" s="63"/>
       <c r="BH31" s="63"/>
@@ -6209,18 +6213,18 @@
       <c r="BN31" s="78"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="158">
+      <c r="A32" s="157">
         <v>13</v>
       </c>
       <c r="B32" s="36"/>
-      <c r="C32" s="198" t="s">
+      <c r="C32" s="190" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="199"/>
-      <c r="E32" s="195" t="s">
+      <c r="D32" s="191"/>
+      <c r="E32" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="196"/>
+      <c r="F32" s="188"/>
       <c r="G32" s="51"/>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -6283,12 +6287,12 @@
       <c r="BN32" s="78"/>
     </row>
     <row r="33" spans="1:66" ht="12" customHeight="1">
-      <c r="A33" s="166"/>
+      <c r="A33" s="163"/>
       <c r="B33" s="36"/>
-      <c r="C33" s="200"/>
-      <c r="D33" s="201"/>
-      <c r="E33" s="190"/>
-      <c r="F33" s="197"/>
+      <c r="C33" s="192"/>
+      <c r="D33" s="193"/>
+      <c r="E33" s="185"/>
+      <c r="F33" s="189"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -6351,18 +6355,18 @@
       <c r="BN33" s="78"/>
     </row>
     <row r="34" spans="1:66" ht="12" customHeight="1">
-      <c r="A34" s="158">
+      <c r="A34" s="157">
         <v>14</v>
       </c>
       <c r="B34" s="36"/>
-      <c r="C34" s="173" t="s">
+      <c r="C34" s="170" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="174"/>
-      <c r="E34" s="193" t="s">
+      <c r="D34" s="171"/>
+      <c r="E34" s="186" t="s">
         <v>46</v>
       </c>
-      <c r="F34" s="194"/>
+      <c r="F34" s="188"/>
       <c r="G34" s="51"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -6425,12 +6429,12 @@
       <c r="BN34" s="78"/>
     </row>
     <row r="35" spans="1:66" ht="12" customHeight="1">
-      <c r="A35" s="166"/>
+      <c r="A35" s="163"/>
       <c r="B35" s="36"/>
-      <c r="C35" s="188"/>
-      <c r="D35" s="172"/>
-      <c r="E35" s="190"/>
-      <c r="F35" s="192"/>
+      <c r="C35" s="183"/>
+      <c r="D35" s="169"/>
+      <c r="E35" s="185"/>
+      <c r="F35" s="189"/>
       <c r="G35" s="51"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -6493,20 +6497,22 @@
       <c r="BN35" s="78"/>
     </row>
     <row r="36" spans="1:66" ht="12" customHeight="1">
-      <c r="A36" s="158">
+      <c r="A36" s="157">
         <v>15</v>
       </c>
       <c r="B36" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="160" t="s">
+      <c r="C36" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="161"/>
-      <c r="E36" s="156" t="s">
+      <c r="D36" s="160"/>
+      <c r="E36" s="155" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="164"/>
+      <c r="F36" s="296" t="s">
+        <v>60</v>
+      </c>
       <c r="G36" s="38"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -6569,12 +6575,12 @@
       <c r="BN36" s="77"/>
     </row>
     <row r="37" spans="1:66" ht="12" customHeight="1">
-      <c r="A37" s="159"/>
+      <c r="A37" s="158"/>
       <c r="B37" s="34"/>
-      <c r="C37" s="162"/>
-      <c r="D37" s="163"/>
-      <c r="E37" s="157"/>
-      <c r="F37" s="165"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="162"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="297"/>
       <c r="G37" s="51"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
@@ -6624,11 +6630,11 @@
       <c r="BA37" s="63"/>
       <c r="BB37" s="13"/>
       <c r="BC37" s="19"/>
-      <c r="BD37" s="155"/>
+      <c r="BD37" s="154"/>
       <c r="BE37" s="63"/>
-      <c r="BF37" s="154"/>
-      <c r="BG37" s="154"/>
-      <c r="BH37" s="154"/>
+      <c r="BF37" s="153"/>
+      <c r="BG37" s="153"/>
+      <c r="BH37" s="153"/>
       <c r="BI37" s="13"/>
       <c r="BJ37" s="19"/>
       <c r="BK37" s="63"/>
@@ -6637,16 +6643,18 @@
       <c r="BN37" s="78"/>
     </row>
     <row r="38" spans="1:66" ht="12" customHeight="1">
-      <c r="A38" s="159"/>
+      <c r="A38" s="158"/>
       <c r="B38" s="34"/>
-      <c r="C38" s="171" t="s">
+      <c r="C38" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="172"/>
-      <c r="E38" s="167" t="s">
+      <c r="D38" s="169"/>
+      <c r="E38" s="164" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="169"/>
+      <c r="F38" s="166" t="s">
+        <v>60</v>
+      </c>
       <c r="G38" s="50"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -6709,12 +6717,12 @@
       <c r="BN38" s="104"/>
     </row>
     <row r="39" spans="1:66" ht="12" customHeight="1">
-      <c r="A39" s="166"/>
+      <c r="A39" s="163"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="162"/>
-      <c r="D39" s="163"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="170"/>
+      <c r="C39" s="161"/>
+      <c r="D39" s="162"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="167"/>
       <c r="G39" s="54"/>
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
@@ -6777,20 +6785,22 @@
       <c r="BN39" s="76"/>
     </row>
     <row r="40" spans="1:66" ht="12" customHeight="1">
-      <c r="A40" s="158">
+      <c r="A40" s="157">
         <v>16</v>
       </c>
-      <c r="B40" s="180" t="s">
+      <c r="B40" s="175" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="184" t="s">
+      <c r="C40" s="179" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="185"/>
-      <c r="E40" s="177" t="s">
+      <c r="D40" s="180"/>
+      <c r="E40" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F40" s="106"/>
+      <c r="F40" s="290" t="s">
+        <v>60</v>
+      </c>
       <c r="G40" s="50"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -6853,12 +6863,12 @@
       <c r="BN40" s="104"/>
     </row>
     <row r="41" spans="1:66" ht="12" customHeight="1">
-      <c r="A41" s="159"/>
-      <c r="B41" s="181"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="183"/>
-      <c r="F41" s="106"/>
+      <c r="A41" s="158"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="181"/>
+      <c r="D41" s="182"/>
+      <c r="E41" s="178"/>
+      <c r="F41" s="291"/>
       <c r="G41" s="51"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -6912,25 +6922,27 @@
       <c r="BE41" s="63"/>
       <c r="BF41" s="63"/>
       <c r="BG41" s="63"/>
-      <c r="BH41" s="154"/>
+      <c r="BH41" s="153"/>
       <c r="BI41" s="13"/>
       <c r="BJ41" s="19"/>
-      <c r="BK41" s="63"/>
+      <c r="BK41" s="153"/>
       <c r="BL41" s="63"/>
       <c r="BM41" s="63"/>
       <c r="BN41" s="78"/>
     </row>
     <row r="42" spans="1:66" ht="12" customHeight="1">
-      <c r="A42" s="159"/>
-      <c r="B42" s="181"/>
-      <c r="C42" s="173" t="s">
+      <c r="A42" s="158"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="170" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="174"/>
-      <c r="E42" s="177" t="s">
+      <c r="D42" s="171"/>
+      <c r="E42" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="F42" s="178"/>
+      <c r="F42" s="298" t="s">
+        <v>60</v>
+      </c>
       <c r="G42" s="50"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -6993,12 +7005,12 @@
       <c r="BN42" s="104"/>
     </row>
     <row r="43" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A43" s="166"/>
-      <c r="B43" s="182"/>
-      <c r="C43" s="175"/>
-      <c r="D43" s="176"/>
-      <c r="E43" s="168"/>
-      <c r="F43" s="179"/>
+      <c r="A43" s="163"/>
+      <c r="B43" s="177"/>
+      <c r="C43" s="172"/>
+      <c r="D43" s="173"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="167"/>
       <c r="G43" s="39"/>
       <c r="H43" s="11"/>
       <c r="I43" s="11"/>
@@ -7083,7 +7095,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="87">
+  <mergeCells count="88">
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="C26:D27"/>
@@ -7163,6 +7175,7 @@
     <mergeCell ref="E40:E41"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="C40:D41"/>
+    <mergeCell ref="F40:F41"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="C36:D37"/>
@@ -7193,67 +7206,67 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="3" customWidth="1"/>
-    <col min="7" max="30" width="3.109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" style="3" customWidth="1"/>
+    <col min="7" max="30" width="3.125" style="3" customWidth="1"/>
     <col min="31" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="238" t="s">
+      <c r="B1" s="227" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="241" t="s">
+      <c r="C1" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="242"/>
-      <c r="E1" s="247" t="s">
+      <c r="D1" s="231"/>
+      <c r="E1" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="250" t="s">
+      <c r="F1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="232"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="233"/>
-      <c r="T1" s="233"/>
-      <c r="U1" s="233"/>
-      <c r="V1" s="233"/>
-      <c r="W1" s="233"/>
-      <c r="X1" s="233"/>
-      <c r="Y1" s="233"/>
-      <c r="Z1" s="233"/>
-      <c r="AA1" s="233"/>
-      <c r="AB1" s="233"/>
-      <c r="AC1" s="233"/>
-      <c r="AD1" s="234"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="222"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="222"/>
+      <c r="M1" s="222"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="222"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="222"/>
+      <c r="S1" s="222"/>
+      <c r="T1" s="222"/>
+      <c r="U1" s="222"/>
+      <c r="V1" s="222"/>
+      <c r="W1" s="222"/>
+      <c r="X1" s="222"/>
+      <c r="Y1" s="222"/>
+      <c r="Z1" s="222"/>
+      <c r="AA1" s="222"/>
+      <c r="AB1" s="222"/>
+      <c r="AC1" s="222"/>
+      <c r="AD1" s="223"/>
     </row>
     <row r="2" spans="1:30" ht="10.5" customHeight="1">
-      <c r="A2" s="236"/>
-      <c r="B2" s="239"/>
-      <c r="C2" s="243"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="251"/>
+      <c r="A2" s="225"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="240"/>
       <c r="G2" s="46">
         <v>22</v>
       </c>
@@ -7328,12 +7341,12 @@
       </c>
     </row>
     <row r="3" spans="1:30" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="237"/>
-      <c r="B3" s="240"/>
-      <c r="C3" s="245"/>
-      <c r="D3" s="246"/>
-      <c r="E3" s="249"/>
-      <c r="F3" s="252"/>
+      <c r="A3" s="226"/>
+      <c r="B3" s="229"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="238"/>
+      <c r="F3" s="241"/>
       <c r="G3" s="48" t="s">
         <v>18</v>
       </c>
@@ -7408,20 +7421,20 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A4" s="259">
+      <c r="A4" s="246">
         <v>1</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="260" t="s">
+      <c r="C4" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="261"/>
-      <c r="E4" s="273" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="258" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="275"/>
+      <c r="F4" s="260"/>
       <c r="G4" s="49"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
@@ -7444,20 +7457,20 @@
       <c r="Z4" s="12"/>
       <c r="AA4" s="18"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="277" t="s">
+      <c r="AC4" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="AD4" s="266" t="s">
+      <c r="AD4" s="251" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A5" s="254"/>
+      <c r="A5" s="243"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="274"/>
-      <c r="F5" s="276"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="261"/>
       <c r="G5" s="50"/>
       <c r="H5" s="31"/>
       <c r="I5" s="9"/>
@@ -7480,22 +7493,22 @@
       <c r="Z5" s="16"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="9"/>
-      <c r="AC5" s="278"/>
-      <c r="AD5" s="267"/>
+      <c r="AC5" s="263"/>
+      <c r="AD5" s="252"/>
     </row>
     <row r="6" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A6" s="253">
+      <c r="A6" s="242">
         <v>2</v>
       </c>
       <c r="B6" s="34"/>
-      <c r="C6" s="203" t="s">
+      <c r="C6" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="174"/>
-      <c r="E6" s="269" t="s">
+      <c r="D6" s="171"/>
+      <c r="E6" s="254" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="271"/>
+      <c r="F6" s="256"/>
       <c r="G6" s="51"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
@@ -7518,16 +7531,16 @@
       <c r="Z6" s="13"/>
       <c r="AA6" s="19"/>
       <c r="AB6" s="7"/>
-      <c r="AC6" s="278"/>
-      <c r="AD6" s="267"/>
+      <c r="AC6" s="263"/>
+      <c r="AD6" s="252"/>
     </row>
     <row r="7" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A7" s="254"/>
+      <c r="A7" s="243"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="270"/>
-      <c r="F7" s="272"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="257"/>
       <c r="G7" s="52"/>
       <c r="H7" s="32"/>
       <c r="I7" s="24"/>
@@ -7550,24 +7563,24 @@
       <c r="Z7" s="25"/>
       <c r="AA7" s="26"/>
       <c r="AB7" s="24"/>
-      <c r="AC7" s="278"/>
-      <c r="AD7" s="267"/>
+      <c r="AC7" s="263"/>
+      <c r="AD7" s="252"/>
     </row>
     <row r="8" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A8" s="158">
+      <c r="A8" s="157">
         <v>3</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="209" t="s">
+      <c r="C8" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="210"/>
-      <c r="E8" s="281" t="s">
+      <c r="D8" s="199"/>
+      <c r="E8" s="266" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="283"/>
+      <c r="F8" s="268"/>
       <c r="G8" s="38"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -7590,16 +7603,16 @@
       <c r="Z8" s="15"/>
       <c r="AA8" s="21"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="278"/>
-      <c r="AD8" s="267"/>
+      <c r="AC8" s="263"/>
+      <c r="AD8" s="252"/>
     </row>
     <row r="9" spans="1:30" ht="13.5" customHeight="1">
-      <c r="A9" s="166"/>
+      <c r="A9" s="163"/>
       <c r="B9" s="37"/>
-      <c r="C9" s="217"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="282"/>
-      <c r="F9" s="284"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="265"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="269"/>
       <c r="G9" s="53"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
@@ -7622,24 +7635,24 @@
       <c r="Z9" s="44"/>
       <c r="AA9" s="45"/>
       <c r="AB9" s="43"/>
-      <c r="AC9" s="278"/>
-      <c r="AD9" s="267"/>
+      <c r="AC9" s="263"/>
+      <c r="AD9" s="252"/>
     </row>
     <row r="10" spans="1:30" ht="12" customHeight="1">
-      <c r="A10" s="159">
+      <c r="A10" s="158">
         <v>4</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="228" t="s">
+      <c r="C10" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="229"/>
-      <c r="E10" s="285" t="s">
+      <c r="D10" s="218"/>
+      <c r="E10" s="270" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="287"/>
+      <c r="F10" s="272"/>
       <c r="G10" s="50"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -7662,16 +7675,16 @@
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="9"/>
-      <c r="AC10" s="278"/>
-      <c r="AD10" s="267"/>
+      <c r="AC10" s="263"/>
+      <c r="AD10" s="252"/>
     </row>
     <row r="11" spans="1:30" ht="12" customHeight="1">
-      <c r="A11" s="166"/>
+      <c r="A11" s="163"/>
       <c r="B11" s="36"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="212"/>
-      <c r="E11" s="286"/>
-      <c r="F11" s="288"/>
+      <c r="C11" s="200"/>
+      <c r="D11" s="201"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="273"/>
       <c r="G11" s="50"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -7694,22 +7707,22 @@
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="9"/>
-      <c r="AC11" s="278"/>
-      <c r="AD11" s="267"/>
+      <c r="AC11" s="263"/>
+      <c r="AD11" s="252"/>
     </row>
     <row r="12" spans="1:30" ht="12" customHeight="1">
-      <c r="A12" s="158">
+      <c r="A12" s="157">
         <v>5</v>
       </c>
       <c r="B12" s="36"/>
-      <c r="C12" s="203" t="s">
+      <c r="C12" s="195" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="174"/>
-      <c r="E12" s="289" t="s">
+      <c r="D12" s="171"/>
+      <c r="E12" s="274" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="290"/>
+      <c r="F12" s="275"/>
       <c r="G12" s="51"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -7732,16 +7745,16 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="7"/>
-      <c r="AC12" s="278"/>
-      <c r="AD12" s="267"/>
+      <c r="AC12" s="263"/>
+      <c r="AD12" s="252"/>
     </row>
     <row r="13" spans="1:30" ht="12" customHeight="1">
-      <c r="A13" s="159"/>
+      <c r="A13" s="158"/>
       <c r="B13" s="36"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="285"/>
-      <c r="F13" s="287"/>
+      <c r="C13" s="181"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="270"/>
+      <c r="F13" s="272"/>
       <c r="G13" s="52"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
@@ -7764,24 +7777,24 @@
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="24"/>
-      <c r="AC13" s="278"/>
-      <c r="AD13" s="267"/>
+      <c r="AC13" s="263"/>
+      <c r="AD13" s="252"/>
     </row>
     <row r="14" spans="1:30" ht="12" customHeight="1">
-      <c r="A14" s="202">
+      <c r="A14" s="194">
         <v>6</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="184" t="s">
+      <c r="C14" s="179" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="185"/>
-      <c r="E14" s="291" t="s">
+      <c r="D14" s="180"/>
+      <c r="E14" s="276" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="283"/>
+      <c r="F14" s="268"/>
       <c r="G14" s="38"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -7804,16 +7817,16 @@
       <c r="Z14" s="15"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="6"/>
-      <c r="AC14" s="278"/>
-      <c r="AD14" s="267"/>
+      <c r="AC14" s="263"/>
+      <c r="AD14" s="252"/>
     </row>
     <row r="15" spans="1:30" ht="12" customHeight="1">
-      <c r="A15" s="202"/>
+      <c r="A15" s="194"/>
       <c r="B15" s="36"/>
-      <c r="C15" s="188"/>
-      <c r="D15" s="172"/>
-      <c r="E15" s="286"/>
-      <c r="F15" s="288"/>
+      <c r="C15" s="183"/>
+      <c r="D15" s="169"/>
+      <c r="E15" s="271"/>
+      <c r="F15" s="273"/>
       <c r="G15" s="52"/>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
@@ -7836,22 +7849,22 @@
       <c r="Z15" s="25"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="24"/>
-      <c r="AC15" s="278"/>
-      <c r="AD15" s="267"/>
+      <c r="AC15" s="263"/>
+      <c r="AD15" s="252"/>
     </row>
     <row r="16" spans="1:30" ht="12" customHeight="1">
-      <c r="A16" s="202">
+      <c r="A16" s="194">
         <v>7</v>
       </c>
       <c r="B16" s="36"/>
-      <c r="C16" s="203" t="s">
+      <c r="C16" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="174"/>
-      <c r="E16" s="292" t="s">
+      <c r="D16" s="171"/>
+      <c r="E16" s="277" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="290"/>
+      <c r="F16" s="275"/>
       <c r="G16" s="51"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -7874,16 +7887,16 @@
       <c r="Z16" s="13"/>
       <c r="AA16" s="19"/>
       <c r="AB16" s="7"/>
-      <c r="AC16" s="278"/>
-      <c r="AD16" s="267"/>
+      <c r="AC16" s="263"/>
+      <c r="AD16" s="252"/>
     </row>
     <row r="17" spans="1:30" ht="12" customHeight="1">
-      <c r="A17" s="202"/>
+      <c r="A17" s="194"/>
       <c r="B17" s="36"/>
-      <c r="C17" s="188"/>
-      <c r="D17" s="172"/>
-      <c r="E17" s="286"/>
-      <c r="F17" s="288"/>
+      <c r="C17" s="183"/>
+      <c r="D17" s="169"/>
+      <c r="E17" s="271"/>
+      <c r="F17" s="273"/>
       <c r="G17" s="52"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -7906,22 +7919,22 @@
       <c r="Z17" s="25"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="24"/>
-      <c r="AC17" s="278"/>
-      <c r="AD17" s="267"/>
+      <c r="AC17" s="263"/>
+      <c r="AD17" s="252"/>
     </row>
     <row r="18" spans="1:30" ht="12" customHeight="1">
-      <c r="A18" s="202">
+      <c r="A18" s="194">
         <v>8</v>
       </c>
       <c r="B18" s="36"/>
-      <c r="C18" s="203" t="s">
+      <c r="C18" s="195" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="174"/>
-      <c r="E18" s="292" t="s">
+      <c r="D18" s="171"/>
+      <c r="E18" s="277" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="290"/>
+      <c r="F18" s="275"/>
       <c r="G18" s="52"/>
       <c r="H18" s="24"/>
       <c r="I18" s="24"/>
@@ -7944,16 +7957,16 @@
       <c r="Z18" s="25"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="24"/>
-      <c r="AC18" s="278"/>
-      <c r="AD18" s="267"/>
+      <c r="AC18" s="263"/>
+      <c r="AD18" s="252"/>
     </row>
     <row r="19" spans="1:30" ht="12" customHeight="1">
-      <c r="A19" s="202"/>
+      <c r="A19" s="194"/>
       <c r="B19" s="37"/>
-      <c r="C19" s="175"/>
-      <c r="D19" s="176"/>
-      <c r="E19" s="282"/>
-      <c r="F19" s="284"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="267"/>
+      <c r="F19" s="269"/>
       <c r="G19" s="54"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -7976,24 +7989,24 @@
       <c r="Z19" s="17"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="278"/>
-      <c r="AD19" s="267"/>
+      <c r="AC19" s="263"/>
+      <c r="AD19" s="252"/>
     </row>
     <row r="20" spans="1:30" ht="12" customHeight="1">
-      <c r="A20" s="158">
+      <c r="A20" s="157">
         <v>9</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="184" t="s">
+      <c r="C20" s="179" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="291" t="s">
+      <c r="D20" s="180"/>
+      <c r="E20" s="276" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="283"/>
+      <c r="F20" s="268"/>
       <c r="G20" s="38"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -8016,18 +8029,18 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="21"/>
       <c r="AB20" s="6"/>
-      <c r="AC20" s="278"/>
-      <c r="AD20" s="267"/>
+      <c r="AC20" s="263"/>
+      <c r="AD20" s="252"/>
     </row>
     <row r="21" spans="1:30" ht="12" customHeight="1">
-      <c r="A21" s="166"/>
+      <c r="A21" s="163"/>
       <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="188"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="288"/>
+      <c r="C21" s="183"/>
+      <c r="D21" s="169"/>
+      <c r="E21" s="271"/>
+      <c r="F21" s="273"/>
       <c r="G21" s="51"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -8050,22 +8063,22 @@
       <c r="Z21" s="13"/>
       <c r="AA21" s="19"/>
       <c r="AB21" s="7"/>
-      <c r="AC21" s="278"/>
-      <c r="AD21" s="267"/>
+      <c r="AC21" s="263"/>
+      <c r="AD21" s="252"/>
     </row>
     <row r="22" spans="1:30" ht="12" customHeight="1">
-      <c r="A22" s="158">
+      <c r="A22" s="157">
         <v>10</v>
       </c>
       <c r="B22" s="36"/>
-      <c r="C22" s="173" t="s">
+      <c r="C22" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="174"/>
-      <c r="E22" s="292" t="s">
+      <c r="D22" s="171"/>
+      <c r="E22" s="277" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="290"/>
+      <c r="F22" s="275"/>
       <c r="G22" s="51"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -8088,16 +8101,16 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="19"/>
       <c r="AB22" s="7"/>
-      <c r="AC22" s="278"/>
-      <c r="AD22" s="267"/>
+      <c r="AC22" s="263"/>
+      <c r="AD22" s="252"/>
     </row>
     <row r="23" spans="1:30" ht="12" customHeight="1">
-      <c r="A23" s="166"/>
+      <c r="A23" s="163"/>
       <c r="B23" s="36"/>
-      <c r="C23" s="188"/>
-      <c r="D23" s="172"/>
-      <c r="E23" s="286"/>
-      <c r="F23" s="288"/>
+      <c r="C23" s="183"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="271"/>
+      <c r="F23" s="273"/>
       <c r="G23" s="51"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -8120,22 +8133,22 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="19"/>
       <c r="AB23" s="7"/>
-      <c r="AC23" s="278"/>
-      <c r="AD23" s="267"/>
+      <c r="AC23" s="263"/>
+      <c r="AD23" s="252"/>
     </row>
     <row r="24" spans="1:30" ht="12" customHeight="1">
-      <c r="A24" s="158">
+      <c r="A24" s="157">
         <v>11</v>
       </c>
       <c r="B24" s="36"/>
-      <c r="C24" s="173" t="s">
+      <c r="C24" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="174"/>
-      <c r="E24" s="292" t="s">
+      <c r="D24" s="171"/>
+      <c r="E24" s="277" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="290"/>
+      <c r="F24" s="275"/>
       <c r="G24" s="52"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -8158,16 +8171,16 @@
       <c r="Z24" s="25"/>
       <c r="AA24" s="26"/>
       <c r="AB24" s="24"/>
-      <c r="AC24" s="278"/>
-      <c r="AD24" s="267"/>
+      <c r="AC24" s="263"/>
+      <c r="AD24" s="252"/>
     </row>
     <row r="25" spans="1:30" ht="12" customHeight="1">
-      <c r="A25" s="166"/>
+      <c r="A25" s="163"/>
       <c r="B25" s="37"/>
-      <c r="C25" s="188"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="286"/>
-      <c r="F25" s="284"/>
+      <c r="C25" s="183"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="271"/>
+      <c r="F25" s="269"/>
       <c r="G25" s="54"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -8190,24 +8203,24 @@
       <c r="Z25" s="17"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="278"/>
-      <c r="AD25" s="267"/>
+      <c r="AC25" s="263"/>
+      <c r="AD25" s="252"/>
     </row>
     <row r="26" spans="1:30" ht="12" customHeight="1">
-      <c r="A26" s="253">
+      <c r="A26" s="242">
         <v>12</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="160" t="s">
+      <c r="C26" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="161"/>
-      <c r="E26" s="293" t="s">
+      <c r="D26" s="160"/>
+      <c r="E26" s="278" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="295"/>
+      <c r="F26" s="280"/>
       <c r="G26" s="38"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
@@ -8230,16 +8243,16 @@
       <c r="Z26" s="15"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="6"/>
-      <c r="AC26" s="278"/>
-      <c r="AD26" s="267"/>
+      <c r="AC26" s="263"/>
+      <c r="AD26" s="252"/>
     </row>
     <row r="27" spans="1:30" ht="12" customHeight="1">
-      <c r="A27" s="254"/>
+      <c r="A27" s="243"/>
       <c r="B27" s="34"/>
-      <c r="C27" s="162"/>
-      <c r="D27" s="163"/>
-      <c r="E27" s="294"/>
-      <c r="F27" s="296"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="279"/>
+      <c r="F27" s="281"/>
       <c r="G27" s="51"/>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -8262,24 +8275,24 @@
       <c r="Z27" s="13"/>
       <c r="AA27" s="19"/>
       <c r="AB27" s="7"/>
-      <c r="AC27" s="278"/>
-      <c r="AD27" s="267"/>
+      <c r="AC27" s="263"/>
+      <c r="AD27" s="252"/>
     </row>
     <row r="28" spans="1:30" ht="12" customHeight="1">
-      <c r="A28" s="253">
+      <c r="A28" s="242">
         <v>14</v>
       </c>
-      <c r="B28" s="298" t="s">
+      <c r="B28" s="283" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="184" t="s">
+      <c r="C28" s="179" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="185"/>
-      <c r="E28" s="298" t="s">
+      <c r="D28" s="180"/>
+      <c r="E28" s="283" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="302"/>
+      <c r="F28" s="287"/>
       <c r="G28" s="38"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -8302,16 +8315,16 @@
       <c r="Z28" s="15"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="40"/>
-      <c r="AC28" s="278"/>
-      <c r="AD28" s="267"/>
+      <c r="AC28" s="263"/>
+      <c r="AD28" s="252"/>
     </row>
     <row r="29" spans="1:30" ht="12" customHeight="1" thickBot="1">
-      <c r="A29" s="297"/>
-      <c r="B29" s="299"/>
-      <c r="C29" s="300"/>
-      <c r="D29" s="301"/>
-      <c r="E29" s="299"/>
-      <c r="F29" s="303"/>
+      <c r="A29" s="282"/>
+      <c r="B29" s="284"/>
+      <c r="C29" s="285"/>
+      <c r="D29" s="286"/>
+      <c r="E29" s="284"/>
+      <c r="F29" s="288"/>
       <c r="G29" s="39"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
@@ -8334,8 +8347,8 @@
       <c r="Z29" s="14"/>
       <c r="AA29" s="20"/>
       <c r="AB29" s="11"/>
-      <c r="AC29" s="279"/>
-      <c r="AD29" s="268"/>
+      <c r="AC29" s="264"/>
+      <c r="AD29" s="253"/>
     </row>
     <row r="30" spans="1:30">
       <c r="Z30" s="5"/>
